--- a/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Dictionary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_KPI_Target'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_KPI_Target'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Calendar'!$A$1:$AP$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Content'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Approval'!$A$1:$R$2</definedName>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -534,20 +534,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Tên cột</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Là TEXT THUẦN, không có icon — trùng khớp tuyệt đối với tên trong schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>LUẬT VÀNG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Ô nền VÀNG ở hàng tiêu đề là cột của bạn — agent không bao giờ ghi đè.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH LÁ do script sinh — sửa tay sẽ bị ghi đè lần chạy sau.</t>
+          <t>Nền VÀNG ở hàng tiêu đề = CỦA BẠN — agent không bao giờ ghi đè.</t>
         </is>
       </c>
     </row>
@@ -555,23 +559,23 @@
       <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH DƯƠNG do agent sinh — bạn sửa thoải mái.</t>
+          <t>Nền XANH LÁ = script sinh, sửa tay sẽ bị ghi đè.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nền XANH DƯƠNG = agent sinh, bạn sửa thoải mái.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Ô rỗng nghĩa là gì</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+          <t>Không nhớ màu? Mở sheet _Dictionary, cột 'ai ghi'.</t>
         </is>
       </c>
     </row>
@@ -582,140 +586,156 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>Ô rỗng nghĩa là gì</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>01_Brief</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 trường của brief — Thay cho brief.yml. Brief là thứ BẠN duyệt nên phải nằm trong workbook, không nằm ở file cấu hình máy đọc.
 </t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>02_KPI_Target</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = campaign × kênh × pillar × chỉ số × kỳ — baseline_n &lt; 10 thì mọi so-sánh-với-median phải bị chặn. Đây là chỗ duy nhất giữ con số baseline — không được nhân bản sang sheet khác.
 </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>03_Calendar</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset — Sheet trung tâm. Nhìn hết một chiến dịch trên một màn hình.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>04_Content</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 mảnh nội dung × 1 biến thể — Tách khỏi Calendar vì một asset có nhiều mảnh nội dung (title A/B, 3 caption, prompt media) và vì text dài làm dòng Calendar cao vài trăm pixel.
 </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>05_Approval</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 vòng duyệt — Tách khỏi Calendar vì một asset duyệt nhiều vòng. Gộp một dòng là mất lịch sử revise — thứ đắt nhất khi rà lại sau chiến dịch.
 </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>06_Publish_Log</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset × 1 kênh × 1 lần chạy — Vết của mọi lần publish, kể cả dry-run và lần lỗi.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>07_Metrics_Daily</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = asset × kênh × ngày — Bản nạp lại của RIÊNG chiến dịch này (≈1.700 dòng cho 31 asset × 2 kênh × 28 ngày) để soi được ngay trong file. Nguồn sự thật vẫn là CSV ở data/&lt;instance&gt;/raw|star.
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>08_Metrics_Summary</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>09_Leads</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>08_Metrics_Summary</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>09_Leads</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>10_Insights</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 phát hiện — Ép insight phải có bằng chứng. Không có evidence_metric + evidence_value thì không được ghi dòng — đây là chỗ AI hay bịa nhất.
 </t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Làm mới workbook</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>python scripts/workbook/build_workbook.py --campaign-id &lt;ID&gt; --out &lt;file&gt;</t>
         </is>
@@ -756,82 +776,82 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_id</t>
+          <t>lead_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source_raw</t>
+          <t>source_raw</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ created_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ need_type</t>
+          <t>need_type</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ product_interest</t>
+          <t>product_interest</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ region</t>
+          <t>region</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ branch</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_status</t>
+          <t>lead_status</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ priority_score</t>
+          <t>priority_score</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_segment</t>
+          <t>lead_segment</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ next_action</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_duplicate_of</t>
+          <t>is_duplicate_of</t>
         </is>
       </c>
     </row>
@@ -877,72 +897,72 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 insight_id</t>
+          <t>insight_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope_ref</t>
+          <t>scope_ref</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 observed_at</t>
+          <t>observed_at</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 symptom</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_metric</t>
+          <t>evidence_metric</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_value</t>
+          <t>evidence_value</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_value</t>
+          <t>baseline_value</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 likely_cause</t>
+          <t>likely_cause</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 impact</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recommendation</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 priority</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 status</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6899,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6917,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6939,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6957,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6971,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6989,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6987,7 +7007,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7021,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7037,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7053,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7071,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7063,13 +7083,13 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Số hồ sơ vay</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7081,13 +7101,13 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chi phí trên mỗi lead (CPL)</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7121,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7135,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7149,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7163,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7183,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7197,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7211,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7225,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7239,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7257,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>🤖 agent</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7275,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7288,1489 +7308,57 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 metric_name</t>
+          <t>metric_name</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 period</t>
+          <t>period</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 target_value</t>
+          <t>target_value</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 unit</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_median</t>
+          <t>baseline_median</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_source</t>
+          <t>baseline_source</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_n</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10334</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>12321</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9937</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4525</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>9937</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4525</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4783</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>11924</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4783</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4783</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Testimonial</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6359</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1533</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Testimonial</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1533</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fb_post_summary_median</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4372</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5465</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>5465</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1278</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1278</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Testimonial</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>người</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>youtube_export_median</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HowTo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Testimonial</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Testimonial</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>baseline_n</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J33"/>
+  <autoFilter ref="A1:J2"/>
   <dataValidations count="2">
     <dataValidation sqref="A2:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài enum" error="Giá trị phải nằm trong danh sách platform" type="list">
       <formula1>'_Lists'!$A$2:$A$200</formula1>
@@ -8839,212 +7427,212 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 series_id</t>
+          <t>series_id</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 episode_no</t>
+          <t>episode_no</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 week_no</t>
+          <t>week_no</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 parent_asset_id</t>
+          <t>parent_asset_id</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 doc_ref</t>
+          <t>doc_ref</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_primary</t>
+          <t>pillar_primary</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_secondary</t>
+          <t>pillar_secondary</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 persona_target</t>
+          <t>persona_target</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>🤖 distribution_platforms</t>
+          <t>distribution_platforms</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>🤖 funnel_stage</t>
+          <t>funnel_stage</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>🤖 function_role</t>
+          <t>function_role</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_draft</t>
+          <t>title_draft</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_final</t>
+          <t>title_final</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>🤖 cta_type</t>
+          <t>cta_type</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>🤖 has_commercial_cta</t>
+          <t>has_commercial_cta</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ hashtag_count</t>
+          <t>hashtag_count</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_date</t>
+          <t>planned_publish_date</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_time</t>
+          <t>planned_publish_time</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
-          <t>🤖 timezone</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="Y1" s="9" t="inlineStr">
         <is>
-          <t>👤 tos_score</t>
+          <t>tos_score</t>
         </is>
       </c>
       <c r="Z1" s="9" t="inlineStr">
         <is>
-          <t>👤 hrs_score</t>
+          <t>hrs_score</t>
         </is>
       </c>
       <c r="AA1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_topic</t>
+          <t>approve_topic</t>
         </is>
       </c>
       <c r="AB1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_content</t>
+          <t>approve_content</t>
         </is>
       </c>
       <c r="AC1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_final</t>
+          <t>approve_final</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>🤖 status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
         <is>
-          <t>🤖 owner</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="AF1" s="8" t="inlineStr">
         <is>
-          <t>🤖 verification_open</t>
+          <t>verification_open</t>
         </is>
       </c>
       <c r="AG1" s="9" t="inlineStr">
         <is>
-          <t>👤 qa_passed</t>
+          <t>qa_passed</t>
         </is>
       </c>
       <c r="AH1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="AI1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_at</t>
+          <t>approved_at</t>
         </is>
       </c>
       <c r="AJ1" s="8" t="inlineStr">
         <is>
-          <t>🤖 blocked_reason</t>
+          <t>blocked_reason</t>
         </is>
       </c>
       <c r="AK1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ actual_publish_datetime</t>
+          <t>actual_publish_datetime</t>
         </is>
       </c>
       <c r="AL1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="AM1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="AN1" s="8" t="inlineStr">
         <is>
-          <t>🤖 playlist_id</t>
+          <t>playlist_id</t>
         </is>
       </c>
       <c r="AO1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_source_id</t>
+          <t>recycle_source_id</t>
         </is>
       </c>
       <c r="AP1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_due_date</t>
+          <t>recycle_due_date</t>
         </is>
       </c>
     </row>
@@ -11403,62 +9991,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_id</t>
+          <t>content_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_type</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 variant</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 body</t>
+          <t>body</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ char_count</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 language</t>
+          <t>language</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 draft_path</t>
+          <t>draft_path</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 ai_generated</t>
+          <t>ai_generated</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ generated_at</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 is_selected</t>
+          <t>is_selected</t>
         </is>
       </c>
     </row>
@@ -11514,92 +10102,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>👤 review_id</t>
+          <t>review_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>👤 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>👤 round_no</t>
+          <t>round_no</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 submitted_at</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>👤 reviewer</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 decided_at</t>
+          <t>decided_at</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>👤 comment</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_primary_source</t>
+          <t>chk_primary_source</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_fact_opinion</t>
+          <t>chk_fact_opinion</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_title_no_overclaim</t>
+          <t>chk_title_no_overclaim</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_thumbnail_honest</t>
+          <t>chk_thumbnail_honest</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_subscribe_reason</t>
+          <t>chk_subscribe_reason</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_next_bridge</t>
+          <t>chk_next_bridge</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_hashtag_ok</t>
+          <t>chk_hashtag_ok</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_cta_ok</t>
+          <t>chk_cta_ok</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_internal_tool</t>
+          <t>chk_no_internal_tool</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_pii</t>
+          <t>chk_no_pii</t>
         </is>
       </c>
     </row>
@@ -11670,62 +10258,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ run_id</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ attempt_no</t>
+          <t>attempt_no</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ mode</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ autonomy_at_run</t>
+          <t>autonomy_at_run</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ requested_at</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ scheduled_for</t>
+          <t>scheduled_for</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ error_message</t>
+          <t>error_message</t>
         </is>
       </c>
     </row>
@@ -11790,137 +10378,137 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ date</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ impressions</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_organic</t>
+          <t>reach_organic</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_paid</t>
+          <t>reach_paid</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ views</t>
+          <t>views</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engaged_views</t>
+          <t>engaged_views</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_view_duration_sec</t>
+          <t>avg_view_duration_sec</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_percentage_viewed</t>
+          <t>avg_percentage_viewed</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ watch_time_min</t>
+          <t>watch_time_min</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ likes</t>
+          <t>likes</t>
         </is>
       </c>
       <c r="Q1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="R1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ shares</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="S1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_total</t>
+          <t>engagement_total</t>
         </is>
       </c>
       <c r="T1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ poll_votes</t>
+          <t>poll_votes</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subscribers_gained</t>
+          <t>subscribers_gained</t>
         </is>
       </c>
       <c r="V1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ related_video_clicks</t>
+          <t>related_video_clicks</t>
         </is>
       </c>
       <c r="W1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ returning_viewers</t>
+          <t>returning_viewers</t>
         </is>
       </c>
       <c r="X1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ clicks_total</t>
+          <t>clicks_total</t>
         </is>
       </c>
       <c r="Y1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_clicks</t>
+          <t>cta_clicks</t>
         </is>
       </c>
       <c r="Z1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ leads</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="AA1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cost</t>
+          <t>cost</t>
         </is>
       </c>
     </row>
@@ -11970,92 +10558,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m24h_views</t>
+          <t>m24h_views</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m72h_views</t>
+          <t>m72h_views</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m7d_views</t>
+          <t>m7d_views</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m28d_views</t>
+          <t>m28d_views</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_rate</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_rate</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subs_per_1000_engaged</t>
+          <t>subs_per_1000_engaged</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_primary</t>
+          <t>vs_median_primary</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_secondary</t>
+          <t>vs_median_secondary</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ kpi_hit_count</t>
+          <t>kpi_hit_count</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ guardrail_ok</t>
+          <t>guardrail_ok</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_winner</t>
+          <t>is_winner</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_28d</t>
+          <t>decision_28d</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_note</t>
+          <t>decision_note</t>
         </is>
       </c>
     </row>

--- a/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
@@ -22,12 +22,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Links" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Cost" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Activity_Log" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Dictionary" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Platform_Sync" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Dictionary" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_KPI_Target'!$A$1:$J$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Calendar'!$A$1:$AP$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Calendar'!$A$1:$AQ$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Content'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Approval'!$A$1:$R$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_Publish_Log'!$A$1:$L$2</definedName>
@@ -39,7 +40,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_Links'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'13_Cost'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_Activity_Log'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'_Dictionary'!$A$1:$G$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'15_Platform_Sync'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'_Dictionary'!$A$1:$G$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +52,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +63,13 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -95,10 +104,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,9 +137,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -492,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -784,16 +796,29 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 dòng = 1 asset × 1 nền tảng — Cầu nối duy nhất giữa asset của mình và bài thật trên nền tảng. Quy trình đồng bộ: (1) đăng xong → ghi platform_post_id vào đây · (2) tải export hoặc gọi API · (3) nối theo platform_post_id → 07_Metrics_Daily · (4) đóng dấu last_synced_at. Chưa có dòng ở đây thì asset chưa được coi là đã đo, dù có số liệu ở đâu đó.
+</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Làm mới workbook</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>python scripts/workbook/build_workbook.py --campaign-id &lt;ID&gt; --out &lt;file&gt;</t>
         </is>
@@ -1150,7 +1175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F-6119569e</t>
+          <t>F-237cc7d6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1160,25 +1185,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>markdown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>infographic</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>assets/images/P-Q2-16-info.svg</t>
+          <t>caption</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-16/P-Q2-16-caption.md</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>b0d543349c0b1c97</t>
+          <t>d4db48d50e043397</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1186,16 +1213,20 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>2026-07-22 01:15:51</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F-e5f53ff1</t>
+          <t>F-f8cf817b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1210,17 +1241,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>thumbnail</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>assets/images/P-Q2-16-thumb.svg</t>
+          <t>infographic</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-16/P-Q2-16-info.svg</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>217</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>b0d543349c0b1c97</t>
@@ -1231,44 +1264,50 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-22 01:15:51</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F-f1f7b407</t>
+          <t>F-dc129444</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P-Q2-17</t>
+          <t>P-Q2-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>markdown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>thumbnail</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>assets/images/P-Q2-17-thumb.svg</t>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-16/P-Q2-16-script.md</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>217</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>b0d543349c0b1c97</t>
+          <t>1a1969771ebd3472</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1276,16 +1315,20 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>2026-07-22 01:15:51</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F-e8292802</t>
+          <t>F-e1daece0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1295,25 +1338,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>markdown</t>
+          <t>image</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>caption</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>drafts/P-Q2-16-caption.md</t>
+          <t>thumbnail</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-16/P-Q2-16-thumb.svg</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d4db48d50e043397</t>
+          <t>b0d543349c0b1c97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1321,44 +1366,50 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>2026-07-22 01:15:51</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F-5ac6f953</t>
+          <t>F-fe88b90d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P-Q2-16</t>
+          <t>P-Q2-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>markdown</t>
+          <t>image</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>drafts/P-Q2-16-script.md</t>
+          <t>thumbnail</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-17/P-Q2-17-thumb.svg</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1a1969771ebd3472</t>
+          <t>b0d543349c0b1c97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1366,11 +1417,15 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>2026-07-22 01:15:51</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O2"/>
@@ -1388,6 +1443,13 @@
       <formula1>'_Lists'!$C$2:$C$200</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1493,7 +1555,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-01</t>
         </is>
@@ -1518,6 +1580,7 @@
           <t>P-Q2-01</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1530,7 +1593,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1613,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-02</t>
         </is>
@@ -1575,6 +1638,7 @@
           <t>P-Q2-02</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1587,7 +1651,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1671,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-03</t>
         </is>
@@ -1632,6 +1696,7 @@
           <t>P-Q2-03</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1644,7 +1709,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1729,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-04</t>
         </is>
@@ -1689,6 +1754,7 @@
           <t>P-Q2-04</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1701,7 +1767,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1787,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-05</t>
         </is>
@@ -1746,6 +1812,7 @@
           <t>P-Q2-05</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1758,7 +1825,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1845,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-06</t>
         </is>
@@ -1803,6 +1870,7 @@
           <t>P-Q2-06</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1815,7 +1883,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1903,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-07</t>
         </is>
@@ -1860,6 +1928,7 @@
           <t>P-Q2-07</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1872,7 +1941,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1961,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-08</t>
         </is>
@@ -1917,6 +1986,7 @@
           <t>P-Q2-08</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1929,7 +1999,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2019,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-09</t>
         </is>
@@ -1974,6 +2044,7 @@
           <t>P-Q2-09</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1986,7 +2057,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2077,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-09</t>
         </is>
@@ -2031,6 +2102,7 @@
           <t>P-Q2-09</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2043,7 +2115,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2135,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-10</t>
         </is>
@@ -2088,6 +2160,7 @@
           <t>P-Q2-10</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2100,7 +2173,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2193,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-11</t>
         </is>
@@ -2145,6 +2218,7 @@
           <t>P-Q2-11</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2157,7 +2231,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2251,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-12</t>
         </is>
@@ -2202,6 +2276,7 @@
           <t>P-Q2-12</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2214,7 +2289,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2309,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-13</t>
         </is>
@@ -2259,6 +2334,7 @@
           <t>P-Q2-13</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2271,7 +2347,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2367,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-14</t>
         </is>
@@ -2316,6 +2392,7 @@
           <t>P-Q2-14</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2328,7 +2405,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2425,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-15</t>
         </is>
@@ -2373,6 +2450,7 @@
           <t>P-Q2-15</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2385,7 +2463,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2483,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-16</t>
         </is>
@@ -2430,6 +2508,7 @@
           <t>P-Q2-16</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2442,7 +2521,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2541,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-17</t>
         </is>
@@ -2487,6 +2566,7 @@
           <t>P-Q2-17</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2499,7 +2579,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2599,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=youtube&amp;utm_medium=video&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-18</t>
         </is>
@@ -2544,6 +2624,7 @@
           <t>P-Q2-18</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2556,7 +2637,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2657,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-19</t>
         </is>
@@ -2601,6 +2682,7 @@
           <t>P-Q2-19</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2613,7 +2695,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2715,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-20</t>
         </is>
@@ -2658,6 +2740,7 @@
           <t>P-Q2-20</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2670,7 +2753,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2773,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-21</t>
         </is>
@@ -2715,6 +2798,7 @@
           <t>P-Q2-21</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2727,7 +2811,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2831,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-22</t>
         </is>
@@ -2772,6 +2856,7 @@
           <t>P-Q2-22</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2784,7 +2869,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2889,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-23</t>
         </is>
@@ -2829,6 +2914,7 @@
           <t>P-Q2-23</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2841,7 +2927,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2947,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-24</t>
         </is>
@@ -2886,6 +2972,7 @@
           <t>P-Q2-24</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2898,7 +2985,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +3005,7 @@
           <t>CMP-2026-Q2</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback?utm_source=facebook&amp;utm_medium=social&amp;utm_campaign=CMP-2026-Q2&amp;utm_content=P-Q2-25</t>
         </is>
@@ -2943,6 +3030,7 @@
           <t>P-Q2-25</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2955,12 +3043,40 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-22 01:15:51</t>
+          <t>2026-07-22 10:54:18</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3043,7 +3159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3107,218 +3223,6 @@
       <c r="J1" s="10" t="inlineStr">
         <is>
           <t>detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A00001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:16:19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DucNguyen</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>auto-approve:approve_topic</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>duyệt 26, bỏ qua 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A00002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:16:20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DucNguyen</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>auto-approve</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>gate approve_final không auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A00003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:16:55</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DucNguyen</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>auto-approve:approve_topic</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>duyệt 0, bỏ qua 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:17:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DucNguyen</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>auto-approve:approve_topic</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>duyệt 0, bỏ qua 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A00005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-22 01:18:08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DucNguyen</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>auto-approve:approve_topic</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>duyệt 2, bỏ qua 24</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3249,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>asset_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>platform_post_id</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>platform_url</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>platform_title</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>sync_method</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>last_synced_at</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>last_sync_status</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>metrics_from</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>metrics_to</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L2"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài enum" error="Giá trị phải nằm trong danh sách platform" type="list">
+      <formula1>'_Lists'!$Z$2:$Z$200</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài enum" error="Giá trị phải nằm trong danh sách inline_manual_export_api_manual" type="list">
+      <formula1>'_Lists'!$R$2:$R$200</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài enum" error="Giá trị phải nằm trong danh sách inline_ok_not_found_permission_" type="list">
+      <formula1>'_Lists'!$T$2:$T$200</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3371,10 +3377,12 @@
     <col width="33" customWidth="1" min="21" max="21"/>
     <col width="33" customWidth="1" min="22" max="22"/>
     <col width="33" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="24" max="24"/>
+    <col width="33" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3465,50 +3473,60 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>inline_manual_export_api_manual</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>inline_ok_blocked_error_skipped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inline_ok_not_found_permission_</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inline_own_licensed_cc_stock_un</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>inline_queued_scheduled_publish</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>inline_thumbnail_hero_media_b_r</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>inline_title_hook_description_c</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>inline_đề xuất_đã duyệt_đang là</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>lead_segment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>lead_source</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -3602,50 +3620,60 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>own</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>queued</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>thumbnail</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>đề xuất</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>youtube</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idea</t>
         </is>
@@ -3739,50 +3767,60 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>licensed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>scheduled</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>hero_media</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>hook</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>đã duyệt</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>hotline</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>facebook</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>drafted</t>
         </is>
@@ -3866,50 +3904,60 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>error</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>permission_denied</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>cc</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>b_roll</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>đang làm</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>nurture</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>need_review</t>
         </is>
@@ -3961,52 +4009,57 @@
           <t>markdown</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>stale</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>infographic</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>xong</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>low_priority</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>social_inbox</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>newsletter</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4048,37 +4101,42 @@
           <t>doc</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>bỏ</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>scheduled</t>
         </is>
@@ -4105,22 +4163,22 @@
           <t>other</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>media_prompt</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>published</t>
         </is>
@@ -4142,22 +4200,22 @@
           <t>business</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>pinned_comment</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>qr_event</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -4169,17 +4227,17 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>source_data</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>thumbnail_brief</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>archived</t>
         </is>
@@ -4191,17 +4249,17 @@
           <t>none</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>chapters</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>rejected</t>
         </is>
@@ -4212,13 +4270,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5886,17 +5944,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>actual_publish_datetime</t>
+          <t>asset_folder</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>assets/{asset_id}/ — mọi tài liệu của asset này nằm trong đó</t>
         </is>
       </c>
     </row>
@@ -5908,22 +5971,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>platform_native_id</t>
+          <t>actual_publish_datetime</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>YouTube videoId / FB {page}_{post} — khoá kéo analytics</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5993,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>live_url</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5946,6 +6004,11 @@
       <c r="F74" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>YouTube videoId / FB {page}_{post} — khoá kéo analytics</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6020,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>playlist_id</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5967,7 +6030,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6042,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>recycle_source_id</t>
+          <t>playlist_id</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6001,12 +6064,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>recycle_due_date</t>
+          <t>recycle_source_id</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6018,32 +6081,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>04_Content</t>
+          <t>03_Calendar</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>content_id</t>
+          <t>recycle_due_date</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>{asset_id}-{content_type}-{variant}</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6108,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>content_id</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6071,6 +6124,11 @@
       <c r="F79" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{asset_id}-{content_type}-{variant}</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6140,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>title,hook,description,caption,script,media_prompt,pinned_comment,thumbnail_brief,chapters</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6114,7 +6167,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6124,7 +6177,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A,B,final</t>
+          <t>title,hook,description,caption,script,media_prompt,pinned_comment,thumbnail_brief,chapters</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6141,17 +6199,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>A,B,final</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6168,17 +6226,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>char_count</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -6190,17 +6253,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>hashtags</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6275,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6234,7 +6297,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>draft_path</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6245,11 +6308,6 @@
       <c r="F86" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>đường dẫn .md trong drafts/ khi nội dung quá dài cho ô Excel</t>
         </is>
       </c>
     </row>
@@ -6261,17 +6319,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ai_generated</t>
+          <t>draft_path</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>đường dẫn .md trong drafts/ khi nội dung quá dài cho ô Excel</t>
         </is>
       </c>
     </row>
@@ -6283,17 +6346,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>generated_at</t>
+          <t>ai_generated</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -6305,49 +6368,44 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>is_selected</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>biến thể được chọn để đăng</t>
+          <t>script</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05_Approval</t>
+          <t>04_Content</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>review_id</t>
+          <t>is_selected</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>human</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>biến thể được chọn để đăng</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6417,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>review_id</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6386,12 +6444,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>round_no</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6413,17 +6471,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>round_no</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6435,22 +6498,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>reviewer</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6520,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>approval_status_course</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6494,12 +6547,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>decided_at</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>approval_status_course</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6516,12 +6579,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>decided_at</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6538,22 +6601,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>chk_primary_source</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>human</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>có nguồn sơ cấp + ngày sự kiện</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6623,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>chk_fact_opinion</t>
+          <t>chk_primary_source</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6580,7 +6638,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>đã tách FACT / INFERENCE / OPINION</t>
+          <t>có nguồn sơ cấp + ngày sự kiện</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6650,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>chk_title_no_overclaim</t>
+          <t>chk_fact_opinion</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6603,6 +6661,11 @@
       <c r="F100" t="inlineStr">
         <is>
           <t>human</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>đã tách FACT / INFERENCE / OPINION</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6677,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>chk_thumbnail_honest</t>
+          <t>chk_title_no_overclaim</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6625,11 +6688,6 @@
       <c r="F101" t="inlineStr">
         <is>
           <t>human</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>thumbnail không đánh lừa</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6699,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>chk_subscribe_reason</t>
+          <t>chk_thumbnail_honest</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6656,7 +6714,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>có lý do subscribe rõ</t>
+          <t>thumbnail không đánh lừa</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6726,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>chk_next_bridge</t>
+          <t>chk_subscribe_reason</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6683,7 +6741,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>có đường xem tiếp</t>
+          <t>có lý do subscribe rõ</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6753,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>chk_hashtag_ok</t>
+          <t>chk_next_bridge</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6710,7 +6768,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>đúng giới hạn theo kênh</t>
+          <t>có đường xem tiếp</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6780,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>chk_cta_ok</t>
+          <t>chk_hashtag_ok</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6737,7 +6795,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CTA thương mại đúng ngữ cảnh</t>
+          <t>đúng giới hạn theo kênh</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6807,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>chk_no_internal_tool</t>
+          <t>chk_cta_ok</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6764,7 +6822,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>KHÔNG lộ tên công cụ sản xuất nội bộ</t>
+          <t>CTA thương mại đúng ngữ cảnh</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6834,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>chk_no_pii</t>
+          <t>chk_no_internal_tool</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6787,33 +6845,33 @@
       <c r="F107" t="inlineStr">
         <is>
           <t>human</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>KHÔNG lộ tên công cụ sản xuất nội bộ</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06_Publish_Log</t>
+          <t>05_Approval</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>run_id</t>
+          <t>chk_no_pii</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6883,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6852,17 +6910,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>platform</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6884,12 +6937,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>attempt_no</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6906,22 +6969,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>attempt_no</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>dry_run,live</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6938,7 +6991,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>autonomy_at_run</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6948,7 +7001,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>autonomy</t>
+          <t>dry_run,live</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6970,12 +7023,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>requested_at</t>
+          <t>autonomy_at_run</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>autonomy</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6992,7 +7055,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>scheduled_for</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7014,17 +7077,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>scheduled_for</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>queued,scheduled,published,error,skipped</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7041,12 +7099,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>platform_native_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>queued,scheduled,published,error,skipped</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7063,7 +7126,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>live_url</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7085,12 +7148,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7102,22 +7165,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07_Metrics_Daily</t>
+          <t>06_Publish_Log</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>error_message</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7134,17 +7192,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>platform</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7166,12 +7219,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>platform</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7193,17 +7251,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>api,manual_export,sidecar_backfill</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7225,12 +7278,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>impressions</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>api,manual_export,sidecar_backfill</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7247,12 +7310,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ctr</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7269,12 +7332,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>reach</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7291,7 +7354,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>reach_organic</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7313,7 +7376,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>reach_paid</t>
+          <t>reach_organic</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7335,7 +7398,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>views</t>
+          <t>reach_paid</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7357,7 +7420,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>engaged_views</t>
+          <t>views</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7368,11 +7431,6 @@
       <c r="F130" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Shorts: KHÔNG dùng view thô — YouTube đổi cách đếm 31/03/2025</t>
         </is>
       </c>
     </row>
@@ -7384,17 +7442,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>avg_view_duration_sec</t>
+          <t>engaged_views</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Shorts: KHÔNG dùng view thô — YouTube đổi cách đếm 31/03/2025</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7469,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>avg_percentage_viewed</t>
+          <t>avg_view_duration_sec</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7428,7 +7491,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>watch_time_min</t>
+          <t>avg_percentage_viewed</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7450,7 +7513,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>retention_30s</t>
+          <t>watch_time_min</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7461,11 +7524,6 @@
       <c r="F134" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>guardrail của luật winner</t>
         </is>
       </c>
     </row>
@@ -7477,17 +7535,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>likes</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>guardrail của luật winner</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7562,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>likes</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7521,7 +7584,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7543,7 +7606,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>engagement_total</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7565,7 +7628,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>poll_votes</t>
+          <t>engagement_total</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7587,7 +7650,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>subscribers_gained</t>
+          <t>poll_votes</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7609,7 +7672,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>related_video_clicks</t>
+          <t>subscribers_gained</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7631,7 +7694,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>returning_viewers</t>
+          <t>related_video_clicks</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7653,7 +7716,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>clicks_total</t>
+          <t>returning_viewers</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7675,7 +7738,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>cta_clicks</t>
+          <t>clicks_total</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7697,7 +7760,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>leads</t>
+          <t>cta_clicks</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7719,12 +7782,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7736,17 +7799,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>08_Metrics_Summary</t>
+          <t>07_Metrics_Daily</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7763,17 +7826,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>platform</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7790,12 +7848,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>m24h_views</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>platform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7812,7 +7875,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>m72h_views</t>
+          <t>m24h_views</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7834,7 +7897,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>m7d_views</t>
+          <t>m72h_views</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7856,7 +7919,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>m28d_views</t>
+          <t>m7d_views</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7878,12 +7941,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>engagement_rate</t>
+          <t>m28d_views</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7900,7 +7963,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ctr</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7922,7 +7985,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>cta_rate</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7944,7 +8007,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>subs_per_1000_engaged</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7955,11 +8018,6 @@
       <c r="F156" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>★ North Star</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8029,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>retention_30s</t>
+          <t>subs_per_1000_engaged</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7982,6 +8040,11 @@
       <c r="F157" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>★ North Star</t>
         </is>
       </c>
     </row>
@@ -7993,7 +8056,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vs_median_primary</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8004,11 +8067,6 @@
       <c r="F158" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>BLANK nếu baseline_n &lt; 10</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8078,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>vs_median_secondary</t>
+          <t>vs_median_primary</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8031,6 +8089,11 @@
       <c r="F159" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>BLANK nếu baseline_n &lt; 10</t>
         </is>
       </c>
     </row>
@@ -8042,22 +8105,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>kpi_hit_count</t>
+          <t>vs_median_secondary</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>số KPI vượt median</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8127,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>guardrail_ok</t>
+          <t>kpi_hit_count</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8084,7 +8142,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>retention_30s không tụt dưới median</t>
+          <t>số KPI vượt median</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8154,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>is_winner</t>
+          <t>guardrail_ok</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8111,7 +8169,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>kpi_hit_count ≥ min_kpi_count VÀ guardrail_ok</t>
+          <t>retention_30s không tụt dưới median</t>
         </is>
       </c>
     </row>
@@ -8123,22 +8181,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>decision_28d</t>
+          <t>is_winner</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>decision_28d</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>kpi_hit_count ≥ min_kpi_count VÀ guardrail_ok</t>
         </is>
       </c>
     </row>
@@ -8150,12 +8208,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>decision_note</t>
+          <t>decision_28d</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>decision_28d</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8167,27 +8230,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>09_Leads</t>
+          <t>08_Metrics_Summary</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>lead_id</t>
+          <t>decision_note</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -8199,17 +8257,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>lead_id</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>lead_source</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8231,22 +8284,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>source_raw</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>lead_source</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>giá trị gốc trước chuẩn hoá — giữ để truy vết</t>
         </is>
       </c>
     </row>
@@ -8258,22 +8316,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>source_raw</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>giá trị gốc trước chuẩn hoá — giữ để truy vết</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8343,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>campaign_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8307,7 +8370,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8329,7 +8392,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>pillar_code</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8351,7 +8414,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>need_type</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8373,7 +8436,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>product_interest</t>
+          <t>need_type</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8395,7 +8458,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>product_interest</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8417,7 +8480,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8439,7 +8502,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>lead_status</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8461,12 +8524,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>priority_score</t>
+          <t>lead_status</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8483,17 +8546,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>lead_segment</t>
+          <t>priority_score</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>lead_segment</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8510,12 +8568,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>next_action</t>
+          <t>lead_segment</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>lead_segment</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8532,7 +8595,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>is_duplicate_of</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8549,12 +8612,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10_Insights</t>
+          <t>09_Leads</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>insight_id</t>
+          <t>is_duplicate_of</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8562,14 +8625,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -8581,17 +8639,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>insight_id</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>asset,pillar,channel,campaign</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -8613,22 +8666,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>scope_ref</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>asset,pillar,channel,campaign</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>asset_id / pillar_code / platform, tuỳ scope</t>
         </is>
       </c>
     </row>
@@ -8640,22 +8698,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>observed_at</t>
+          <t>scope_ref</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>asset_id / pillar_code / platform, tuỳ scope</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8725,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>observed_at</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8694,12 +8752,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>evidence_metric</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8721,7 +8779,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>evidence_value</t>
+          <t>evidence_metric</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8748,7 +8806,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>baseline_value</t>
+          <t>evidence_value</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8756,9 +8814,14 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -8770,22 +8833,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>likely_cause</t>
+          <t>baseline_value</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>51.01 §13 — bảng triệu chứng→nguyên nhân</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -8797,22 +8855,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>likely_cause</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>cao,trung bình,thấp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>51.01 §13 — bảng triệu chứng→nguyên nhân</t>
         </is>
       </c>
     </row>
@@ -8824,17 +8882,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>cao,trung bình,thấp</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8851,17 +8909,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>P1,P2,P3</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8878,17 +8936,22 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>P1,P2,P3</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -8900,17 +8963,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>đề xuất,đã duyệt,đang làm,xong,bỏ</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8922,27 +8980,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>11_Assets</t>
+          <t>10_Insights</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>file_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>đề xuất,đã duyệt,đang làm,xong,bỏ</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -8954,7 +9012,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>file_id</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8981,17 +9039,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>file_type</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>image,video,audio,markdown,doc,other</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9013,7 +9066,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>file_type</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9023,7 +9076,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>thumbnail,hero_media,b_roll,infographic,script,caption,subtitle,source_data,other</t>
+          <t>image,video,audio,markdown,doc,other</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9040,27 +9098,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>rel_path</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>thumbnail,hero_media,b_roll,infographic,script,caption,subtitle,source_data,other</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>đường dẫn tương đối trong thư mục chiến dịch</t>
         </is>
       </c>
     </row>
@@ -9072,17 +9125,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>bytes</t>
+          <t>rel_path</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>đường dẫn tương đối trong thư mục chiến dịch</t>
         </is>
       </c>
     </row>
@@ -9094,22 +9157,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>dimensions</t>
+          <t>bytes</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>vd 1280x720</t>
         </is>
       </c>
     </row>
@@ -9121,17 +9179,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>duration_sec</t>
+          <t>dimensions</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>vd 1280x720</t>
         </is>
       </c>
     </row>
@@ -9143,22 +9206,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>checksum</t>
+          <t>duration_sec</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>sha256 rút gọn — phát hiện file bị thay mà quên cập nhật</t>
         </is>
       </c>
     </row>
@@ -9170,27 +9228,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>rights_status</t>
+          <t>checksum</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>own,licensed,cc,stock,unknown</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>sha256 rút gọn — phát hiện file bị thay mà quên cập nhật</t>
         </is>
       </c>
     </row>
@@ -9202,22 +9255,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>rights_source</t>
+          <t>rights_status</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>own,licensed,cc,stock,unknown</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>human</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>mua ở đâu / ai chụp / link giấy phép</t>
         </is>
       </c>
     </row>
@@ -9229,17 +9287,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>rights_expiry</t>
+          <t>rights_source</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>human</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>mua ở đâu / ai chụp / link giấy phép</t>
         </is>
       </c>
     </row>
@@ -9251,22 +9314,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ai_generated</t>
+          <t>rights_expiry</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>phải disclose nếu là ảnh chính của bài dài</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -9278,17 +9336,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>ai_generated</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>phải disclose nếu là ảnh chính của bài dài</t>
         </is>
       </c>
     </row>
@@ -9300,12 +9363,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9317,22 +9380,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>12_Links</t>
+          <t>11_Assets</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>link_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
           <t>string</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>có</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9349,7 +9407,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>link_id</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9376,12 +9434,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>campaign_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9398,17 +9461,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>target_url</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
           <t>string</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>có</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9425,7 +9483,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>utm_source</t>
+          <t>target_url</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9452,7 +9510,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>utm_medium</t>
+          <t>utm_source</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9479,7 +9537,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>utm_campaign</t>
+          <t>utm_medium</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9506,7 +9564,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>utm_content</t>
+          <t>utm_campaign</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9514,14 +9572,14 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>agent</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>nên = asset_id để quy ngược được</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9591,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>short_url</t>
+          <t>utm_content</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9544,6 +9602,11 @@
       <c r="F218" t="inlineStr">
         <is>
           <t>agent</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>nên = asset_id để quy ngược được</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9618,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>landing_page</t>
+          <t>short_url</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9577,7 +9640,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>cta_label</t>
+          <t>landing_page</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9599,12 +9662,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>cta_label</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9616,27 +9679,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>13_Cost</t>
+          <t>12_Links</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>cost_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9706,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>campaign_id</t>
+          <t>cost_id</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9675,12 +9733,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9697,22 +9760,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>cost_type</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>ads,production,tool,outsource,other</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9729,12 +9782,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>cost_type</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ads,production,tool,outsource,other</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -9756,12 +9814,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9778,17 +9841,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>spend_date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9805,12 +9863,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>spend_date</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9822,12 +9885,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>14_Activity_Log</t>
+          <t>13_Cost</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>activity_id</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9835,14 +9898,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9912,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>activity_id</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9881,17 +9939,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>actor</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>agent,human,script,schedule</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9913,12 +9966,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>actor_name</t>
+          <t>actor</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>agent,human,script,schedule</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9935,7 +9998,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>actor_name</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9943,19 +10006,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>vd approve · content · publish-log · set</t>
         </is>
       </c>
     </row>
@@ -9967,7 +10020,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>asset_id</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9975,9 +10028,19 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>vd approve · content · publish-log · set</t>
         </is>
       </c>
     </row>
@@ -9989,7 +10052,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10011,27 +10074,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>automation_mode</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>hitl,batch,auto</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
           <t>script</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>chế độ lúc chạy</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10096,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>automation_mode</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10053,17 +10106,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ok,blocked,error,skipped</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>hitl,batch,auto</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
           <t>script</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>chế độ lúc chạy</t>
         </is>
       </c>
     </row>
@@ -10075,22 +10128,373 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ok,blocked,error,skipped</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>14_Activity_Log</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>asset_id</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>platform_post_id</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>FB: {page_id}_{post_id} · YT: videoId 11 ký tự</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>platform_url</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>platform_title</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>tiêu đề ĐANG hiển thị trên nền tảng — lệch với title_final là dấu hiệu ai đó sửa tay</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>giờ nền tảng ghi nhận, có thể lệch giờ lên lịch</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>sync_method</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>manual_export,api,manual_entry</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>last_synced_at</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>last_sync_status</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ok,not_found,permission_denied,stale,error</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>metrics_from</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>khoảng ngày đã có số liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>metrics_to</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>15_Platform_Sync</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G239"/>
+  <autoFilter ref="A1:G252"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11976,7 +12380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP27"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12021,6 +12425,7 @@
     <col width="16" customWidth="1" min="40" max="40"/>
     <col width="16" customWidth="1" min="41" max="41"/>
     <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -12204,32 +12609,37 @@
           <t>blocked_reason</t>
         </is>
       </c>
-      <c r="AK1" s="10" t="inlineStr">
+      <c r="AK1" s="8" t="inlineStr">
+        <is>
+          <t>asset_folder</t>
+        </is>
+      </c>
+      <c r="AL1" s="10" t="inlineStr">
         <is>
           <t>actual_publish_datetime</t>
         </is>
       </c>
-      <c r="AL1" s="10" t="inlineStr">
+      <c r="AM1" s="10" t="inlineStr">
         <is>
           <t>platform_native_id</t>
         </is>
       </c>
-      <c r="AM1" s="10" t="inlineStr">
+      <c r="AN1" s="10" t="inlineStr">
         <is>
           <t>live_url</t>
         </is>
       </c>
-      <c r="AN1" s="8" t="inlineStr">
+      <c r="AO1" s="8" t="inlineStr">
         <is>
           <t>playlist_id</t>
         </is>
       </c>
-      <c r="AO1" s="8" t="inlineStr">
+      <c r="AP1" s="8" t="inlineStr">
         <is>
           <t>recycle_source_id</t>
         </is>
       </c>
-      <c r="AP1" s="8" t="inlineStr">
+      <c r="AQ1" s="8" t="inlineStr">
         <is>
           <t>recycle_due_date</t>
         </is>
@@ -12281,14 +12691,6 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>published</t>
@@ -12297,6 +12699,11 @@
       <c r="AE2" t="inlineStr">
         <is>
           <t>Team Marketing KPIM Bank</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-01/</t>
         </is>
       </c>
     </row>
@@ -12346,14 +12753,6 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="Z3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>published</t>
@@ -12362,6 +12761,11 @@
       <c r="AE3" t="inlineStr">
         <is>
           <t>Team Marketing KPIM Bank</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-02/</t>
         </is>
       </c>
     </row>
@@ -12411,9 +12815,6 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>published</t>
@@ -12422,6 +12823,11 @@
       <c r="AE4" t="inlineStr">
         <is>
           <t>Team Marketing KPIM Bank</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-03/</t>
         </is>
       </c>
     </row>
@@ -12481,6 +12887,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-04/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12538,6 +12949,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-05/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12595,6 +13011,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-06/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12652,6 +13073,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-07/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12709,6 +13135,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-08/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12766,6 +13197,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-09/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12823,6 +13259,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-09/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12880,6 +13321,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-10/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12937,6 +13383,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-11/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12994,6 +13445,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-12/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13051,6 +13507,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-13/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13108,6 +13569,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-14/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13165,6 +13631,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-15/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13222,6 +13693,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK18" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-16/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13279,6 +13755,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK19" s="12" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-17/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13336,6 +13817,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-18/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13393,6 +13879,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-19/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13450,6 +13941,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-20/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13507,6 +14003,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-21/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13564,6 +14065,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-22/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13621,6 +14127,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-23/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13678,6 +14189,11 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-24/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13735,9 +14251,14 @@
           <t>Team Marketing KPIM Bank</t>
         </is>
       </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>assets/P-Q2-25/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP27"/>
+  <autoFilter ref="A1:AQ27"/>
   <dataValidations count="11">
     <dataValidation sqref="K2:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài enum" error="Giá trị phải nằm trong danh sách format" type="list">
       <formula1>'_Lists'!$A$2:$A$200</formula1>
@@ -13773,6 +14294,10 @@
       <formula1>'_Lists'!$A$2:$A$200</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK19" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q2/CMP-2026-Q2.xlsx
@@ -1580,7 +1580,6 @@
           <t>P-Q2-01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1638,7 +1637,6 @@
           <t>P-Q2-02</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1696,7 +1694,6 @@
           <t>P-Q2-03</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1754,7 +1751,6 @@
           <t>P-Q2-04</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1812,7 +1808,6 @@
           <t>P-Q2-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1870,7 +1865,6 @@
           <t>P-Q2-06</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1928,7 +1922,6 @@
           <t>P-Q2-07</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -1986,7 +1979,6 @@
           <t>P-Q2-08</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2044,7 +2036,6 @@
           <t>P-Q2-09</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2102,7 +2093,6 @@
           <t>P-Q2-09</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2160,7 +2150,6 @@
           <t>P-Q2-10</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2218,7 +2207,6 @@
           <t>P-Q2-11</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2276,7 +2264,6 @@
           <t>P-Q2-12</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2334,7 +2321,6 @@
           <t>P-Q2-13</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2392,7 +2378,6 @@
           <t>P-Q2-14</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2450,7 +2435,6 @@
           <t>P-Q2-15</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2508,7 +2492,6 @@
           <t>P-Q2-16</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2566,7 +2549,6 @@
           <t>P-Q2-17</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2624,7 +2606,6 @@
           <t>P-Q2-18</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2682,7 +2663,6 @@
           <t>P-Q2-19</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2740,7 +2720,6 @@
           <t>P-Q2-20</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2798,7 +2777,6 @@
           <t>P-Q2-21</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2856,7 +2834,6 @@
           <t>P-Q2-22</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2914,7 +2891,6 @@
           <t>P-Q2-23</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -2972,7 +2948,6 @@
           <t>P-Q2-24</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -3030,7 +3005,6 @@
           <t>P-Q2-25</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>https://kpimbank.example/lp/cashback</t>
@@ -3087,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3139,6 +3113,806 @@
       <c r="H1" s="9" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C-P-Q2-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C-P-Q2-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C-P-Q2-03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C-P-Q2-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C-P-Q2-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C-P-Q2-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C-P-Q2-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C-P-Q2-08</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C-P-Q2-09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>11681416</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C-P-Q2-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C-P-Q2-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C-P-Q2-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11681416</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C-P-Q2-13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C-P-Q2-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11681416</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C-P-Q2-15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C-P-Q2-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C-P-Q2-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P-Q2-17</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C-P-Q2-18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>15575221</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C-P-Q2-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P-Q2-19</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>11681416</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C-P-Q2-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P-Q2-20</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4867257</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C-P-Q2-21</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P-Q2-21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4867256</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C-P-Q2-22</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P-Q2-22</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4867256</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C-P-Q2-23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>P-Q2-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>11681416</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C-P-Q2-24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>P-Q2-24</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>4867256</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C-P-Q2-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CMP-2026-Q2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>P-Q2-25</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ads</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4867256</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VND</t>
         </is>
       </c>
     </row>
@@ -3249,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3325,6 +4099,894 @@
       <c r="L1" s="9" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3854730219053828</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Vay mua nhà KPIM – lãi suất từ 5,9%/năm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5328778056202055</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vay tới 80% giá trị căn nhà, thời hạn 25 năm</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2350424896090231</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nên vay cố định hay thả nổi? Chọn sao cho đúng</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>atDN9xR-5XH</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nên vay cố định hay thả nổi? Chọn sao cho đúng</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8679415069054753</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chuẩn bị hồ sơ vay mua nhà cần những gì?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8622841753280954</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cách tính khoản trả góp hàng tháng dễ hiểu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DFT6YzpobY0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cách tính khoản trả góp hàng tháng dễ hiểu</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0234061419836835</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ưu đãi mùa mua nhà: miễn phí định giá tài sản</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9595677675060904</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ước tính khoản vay trong 1 phút – dùng thử ngay</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9813898273873357</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Đăng ký vay online và theo dõi hồ sơ trên app</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>afqdMF0WO1O</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Đăng ký vay online và theo dõi hồ sơ trên app</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9571240248592113</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3 bước nộp hồ sơ vay mua nhà 100% online</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oippE2iZNdI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3 bước nộp hồ sơ vay mua nhà 100% online</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9571240248592113</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3 bước nộp hồ sơ vay mua nhà 100% online</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oippE2iZNdI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3 bước nộp hồ sơ vay mua nhà 100% online</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8634981203513142</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Gia đình anh Minh nhận nhà mới sau 3 tuần duyệt vay</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wuzkE6fZFOb</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gia đình anh Minh nhận nhà mới sau 3 tuần duyệt vay</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7121348063197319</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hành trình an cư cùng KPIM của khách hàng trẻ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0226645623268620</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lãi suất ưu đãi cố định 24 tháng – đăng ký sớm</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wACtkUZozLJ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lãi suất ưu đãi cố định 24 tháng – đăng ký sớm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7832522224335881</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Trả nợ linh hoạt, tất toán trước hạn phí thấp</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8696209086327502</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5 sai lầm khi vay mua nhà lần đầu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y4czgvzGD2A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5 sai lầm khi vay mua nhà lần đầu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6030289017256250</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KPIM đồng hành 5.000 gia đình an cư năm qua</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>nhập từ dữ liệu cũ</t>
         </is>
       </c>
     </row>
@@ -14413,7 +16075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14525,6 +16187,3426 @@
       <c r="R1" s="9" t="inlineStr">
         <is>
           <t>chk_no_pii</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P-Q2-01-R1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:22:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P-Q2-01-R1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:29:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P-Q2-01-R1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:36:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P-Q2-02-R1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:43:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P-Q2-02-R1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:50:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P-Q2-02-R1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:57:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P-Q2-03-R1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:04:00</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P-Q2-03-R1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:11:00</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P-Q2-03-R1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:18:00</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P-Q2-04-R1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:25:00</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P-Q2-04-R1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:32:00</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P-Q2-04-R1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:39:00</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P-Q2-05-R1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:46:00</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P-Q2-05-R1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-18 15:53:00</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P-Q2-05-R1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:00:00</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P-Q2-06-R1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:07:00</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P-Q2-06-R1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:14:00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P-Q2-06-R1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:21:00</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P-Q2-07-R1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:28:00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P-Q2-07-R1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:35:00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P-Q2-07-R1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:42:00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P-Q2-08-R1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:49:00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P-Q2-08-R1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:56:00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P-Q2-08-R1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:03:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P-Q2-09-R1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:10:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P-Q2-09-R1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:17:00</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P-Q2-09-R1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:24:00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P-Q2-10-R1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:31:00</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P-Q2-10-R1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:38:00</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P-Q2-10-R1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:45:00</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P-Q2-11-R1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:52:00</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P-Q2-11-R1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:59:00</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P-Q2-11-R1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:06:00</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P-Q2-12-R1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:13:00</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P-Q2-12-R1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:20:00</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P-Q2-12-R1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:27:00</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P-Q2-13-R1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:34:00</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P-Q2-13-R1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:41:00</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P-Q2-13-R1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:48:00</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P-Q2-14-R1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:55:00</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P-Q2-14-R1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:02:00</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P-Q2-14-R1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:09:00</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P-Q2-15-R1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:16:00</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P-Q2-15-R1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:23:00</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P-Q2-15-R1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:30:00</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>P-Q2-16-R1</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:37:00</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>P-Q2-16-R1</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:44:00</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>P-Q2-16-R1</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:51:00</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>P-Q2-17-R1</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>P-Q2-17</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:58:00</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>P-Q2-17-R1</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>P-Q2-17</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:05:00</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>P-Q2-17-R1</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>P-Q2-17</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:12:00</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>P-Q2-18-R1</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>P-Q2-18-R1</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>P-Q2-18-R1</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>P-Q2-19-R1</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>P-Q2-19</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:40:00</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>P-Q2-19-R1</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>P-Q2-19</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:47:00</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>P-Q2-19-R1</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>P-Q2-19</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:54:00</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>P-Q2-20-R1</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>P-Q2-20</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:01:00</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Thiếu dòng 'Điều kiện &amp; điều khoản áp dụng' bắt buộc với bài Promo</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>P-Q2-20-R1</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>P-Q2-20</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:08:00</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Giọng văn quá quảng cáo, chỉnh về tông tư vấn</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>P-Q2-20-R1</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>P-Q2-20</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:15:00</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Con số lãi suất chưa kèm thời hạn hiệu lực</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>P-Q2-21-R1</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>P-Q2-21</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:22:00</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>P-Q2-21-R1</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>P-Q2-21</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:29:00</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>P-Q2-21-R1</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>P-Q2-21</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Need Review</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:36:00</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Chờ Compliance đọc lần 2</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>P-Q2-22-R1</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>P-Q2-22</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:43:00</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>P-Q2-22-R1</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>P-Q2-22</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:50:00</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>P-Q2-22-R1</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>P-Q2-22</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:57:00</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>P-Q2-23-R1</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>P-Q2-23</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:04:00</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Ảnh nháp hiển thị số thẻ khách hàng — vi phạm quy tắc PII</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>P-Q2-23-R1</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>P-Q2-23</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà (Marketing Lead)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:11:00</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Ảnh nháp hiển thị số thẻ khách hàng — vi phạm quy tắc PII</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>P-Q2-23-R1</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>P-Q2-23</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:18:00</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Ảnh nháp hiển thị số thẻ khách hàng — vi phạm quy tắc PII</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>P-Q2-24-R1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>P-Q2-24</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:25:00</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Giọng văn quá quảng cáo, chỉnh về tông tư vấn</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>P-Q2-24-R1</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>P-Q2-24</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:32:00</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Thiếu dòng 'Điều kiện &amp; điều khoản áp dụng' bắt buộc với bài Promo</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>P-Q2-24-R1</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>P-Q2-24</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Lê Minh Châu (Content Lead)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Need Revision</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:39:00</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Con số lãi suất chưa kèm thời hạn hiệu lực</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>P-Q2-25-R1</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>P-Q2-25</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Trần Quốc Anh (Compliance)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:46:00</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>P-Q2-25-R1</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>P-Q2-25</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:53:00</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>P-Q2-25-R1</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>P-Q2-25</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Phạm Hải Yến (Brand)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-07-19 13:00:00</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -14575,7 +19657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14651,6 +19733,1616 @@
       <c r="L1" s="10" t="inlineStr">
         <is>
           <t>error_message</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RUN-2026-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P-Q2-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-20 07:46:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RUN-2026-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P-Q2-02</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-20 07:48:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-02-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RUN-2026-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-20 07:51:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-03-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RUN-2026-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P-Q2-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-20 07:55:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-03-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RUN-2026-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P-Q2-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-20 07:57:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-04-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RUN-2026-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:02:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-05-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RUN-2026-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P-Q2-05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:03:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-05-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RUN-2026-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P-Q2-06</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:06:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-06-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RUN-2026-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P-Q2-07</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:09:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-07-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RUN-2026-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:14:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-08-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RUN-2026-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P-Q2-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:16:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-08-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RUN-2026-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:20:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-09-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RUN-2026-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:22:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-09-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RUN-2026-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:26:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>post_id trùng — đã xử lý ở run trước trong cùng batch: P-Q2-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RUN-2026-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P-Q2-09</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:29:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>post_id trùng — đã xử lý ở run trước trong cùng batch: P-Q2-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RUN-2026-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:31:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-10-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RUN-2026-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P-Q2-10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:34:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-10-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RUN-2026-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P-Q2-11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:38:00</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-11-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RUN-2026-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:39:00</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RUN-2026-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P-Q2-12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:42:00</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-12-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RUN-2026-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P-Q2-13</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:47:00</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-13-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RUN-2026-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:50:00</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-14-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RUN-2026-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P-Q2-14</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:53:00</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-14-youtube.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RUN-2026-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P-Q2-15</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:55:00</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-15-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RUN-2026-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:59:00</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>approval_status = Need Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RUN-2026-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P-Q2-16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:01:00</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>approval_status = Need Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RUN-2026-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P-Q2-17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:03:00</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-17-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RUN-2026-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:07:00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>approval_status = Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RUN-2026-0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P-Q2-18</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:11:00</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>approval_status = Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RUN-2026-0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P-Q2-19</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:14:00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-19-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RUN-2026-0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P-Q2-20</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:15:00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>approval_status = Need Revision</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RUN-2026-0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P-Q2-21</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:20:00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>approval_status = Need Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RUN-2026-0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P-Q2-22</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:23:00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-22-facebook.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RUN-2026-0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P-Q2-23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:24:00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>approval_status = Rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RUN-2026-0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P-Q2-24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:29:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>need_review</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>approval_status = Need Revision</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RUN-2026-0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P-Q2-25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>dry_run</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:30:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>drafted</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://drive.kpim.example/drafts/P-Q2-25-facebook.docx</t>
         </is>
       </c>
     </row>
